--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database (wip)/3. autonomous_db_owner (wip)/4. dml/5. binding_area [36,50-53,5]/52. job_history_wip.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database (wip)/3. autonomous_db_owner (wip)/4. dml/5. binding_area [36,50-53,5]/52. job_history_wip.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dproc\Desktop\Disertatie Gabi\2. Workspace\dml\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github_projects\Tech_Hunt_Engine\2. Components\2.1. Cloud Component\2.1.1. Autonomous_Database (wip)\3. autonomous_db_owner (wip)\4. dml\5. binding_area [36,50-53,5]\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FA6255-52C0-4F91-93A4-742BFD110138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D1F1A9-9EAE-43BF-B55A-9907DD9F947E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-84" yWindow="0" windowWidth="10116" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -78,9 +78,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -367,14 +366,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F68"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -394,14 +394,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>43160</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>43646</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>1100</v>
       </c>
       <c r="D2">
@@ -414,14 +414,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>43647</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>44196</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>1400</v>
       </c>
       <c r="D3">
@@ -434,14 +434,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>44211</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>44681</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>1700</v>
       </c>
       <c r="D4">
@@ -454,14 +454,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>43862</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>44227</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>1000</v>
       </c>
       <c r="D5">
@@ -474,14 +474,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>44682</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>45169</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>2200</v>
       </c>
       <c r="D6">
@@ -494,14 +494,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>42979</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>43465</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>900</v>
       </c>
       <c r="D7">
@@ -514,14 +514,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>43475</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>43905</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>1200</v>
       </c>
       <c r="D8">
@@ -534,14 +534,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>44348</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>44957</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>1900</v>
       </c>
       <c r="D9">
@@ -554,14 +554,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>42461</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>43039</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>800</v>
       </c>
       <c r="D10">
@@ -574,14 +574,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>44958</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>45443</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>2500</v>
       </c>
       <c r="D11">
@@ -594,9 +594,1145 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>42979</v>
+      </c>
+      <c r="B12" s="1">
+        <v>43465</v>
+      </c>
+      <c r="C12" s="2">
+        <v>900</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>9</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>43475</v>
+      </c>
+      <c r="B13" s="1">
+        <v>43905</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D13">
+        <v>7</v>
+      </c>
+      <c r="E13">
+        <v>9</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>44211</v>
+      </c>
+      <c r="B14" s="1">
+        <v>44681</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1700</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>8</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>43862</v>
+      </c>
+      <c r="B15" s="1">
+        <v>44227</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>8</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>43160</v>
+      </c>
+      <c r="B16" s="1">
+        <v>43646</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1100</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>8</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>43647</v>
+      </c>
+      <c r="B17" s="1">
+        <v>44196</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1400</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>9</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>44211</v>
+      </c>
+      <c r="B18" s="1">
+        <v>44681</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1700</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>43862</v>
+      </c>
+      <c r="B19" s="1">
+        <v>44227</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>44682</v>
+      </c>
+      <c r="B20" s="1">
+        <v>45169</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2200</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20">
+        <v>9</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>42979</v>
+      </c>
+      <c r="B21" s="1">
+        <v>43465</v>
+      </c>
+      <c r="C21" s="2">
+        <v>900</v>
+      </c>
+      <c r="D21">
+        <v>6</v>
+      </c>
+      <c r="E21">
+        <v>9</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>43475</v>
+      </c>
+      <c r="B22" s="1">
+        <v>43905</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D22">
+        <v>7</v>
+      </c>
+      <c r="E22">
+        <v>9</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>44348</v>
+      </c>
+      <c r="B23" s="1">
+        <v>44957</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1900</v>
+      </c>
+      <c r="D23">
+        <v>8</v>
+      </c>
+      <c r="E23">
+        <v>8</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>42461</v>
+      </c>
+      <c r="B24" s="1">
+        <v>43039</v>
+      </c>
+      <c r="C24" s="2">
+        <v>800</v>
+      </c>
+      <c r="D24">
+        <v>9</v>
+      </c>
+      <c r="E24">
+        <v>9</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>44958</v>
+      </c>
+      <c r="B25" s="1">
+        <v>45443</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2500</v>
+      </c>
+      <c r="D25">
+        <v>10</v>
+      </c>
+      <c r="E25">
+        <v>9</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>42979</v>
+      </c>
+      <c r="B26" s="1">
+        <v>43465</v>
+      </c>
+      <c r="C26" s="2">
+        <v>900</v>
+      </c>
+      <c r="D26">
+        <v>6</v>
+      </c>
+      <c r="E26">
+        <v>9</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>43475</v>
+      </c>
+      <c r="B27" s="1">
+        <v>43905</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D27">
+        <v>7</v>
+      </c>
+      <c r="E27">
+        <v>9</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>44211</v>
+      </c>
+      <c r="B28" s="1">
+        <v>44681</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1700</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28">
+        <v>8</v>
+      </c>
+      <c r="F28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>43862</v>
+      </c>
+      <c r="B29" s="1">
+        <v>44227</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>8</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>42979</v>
+      </c>
+      <c r="B30" s="1">
+        <v>43465</v>
+      </c>
+      <c r="C30" s="2">
+        <v>900</v>
+      </c>
+      <c r="D30">
+        <v>6</v>
+      </c>
+      <c r="E30">
+        <v>9</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>43475</v>
+      </c>
+      <c r="B31" s="1">
+        <v>43905</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D31">
+        <v>7</v>
+      </c>
+      <c r="E31">
+        <v>9</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>44348</v>
+      </c>
+      <c r="B32" s="1">
+        <v>44957</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1900</v>
+      </c>
+      <c r="D32">
+        <v>8</v>
+      </c>
+      <c r="E32">
+        <v>8</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>42461</v>
+      </c>
+      <c r="B33" s="1">
+        <v>43039</v>
+      </c>
+      <c r="C33" s="2">
+        <v>800</v>
+      </c>
+      <c r="D33">
+        <v>9</v>
+      </c>
+      <c r="E33">
+        <v>9</v>
+      </c>
+      <c r="F33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>44958</v>
+      </c>
+      <c r="B34" s="1">
+        <v>45443</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2500</v>
+      </c>
+      <c r="D34">
+        <v>10</v>
+      </c>
+      <c r="E34">
+        <v>9</v>
+      </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>42979</v>
+      </c>
+      <c r="B35" s="1">
+        <v>43465</v>
+      </c>
+      <c r="C35" s="2">
+        <v>900</v>
+      </c>
+      <c r="D35">
+        <v>6</v>
+      </c>
+      <c r="E35">
+        <v>9</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>43475</v>
+      </c>
+      <c r="B36" s="1">
+        <v>43905</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D36">
+        <v>7</v>
+      </c>
+      <c r="E36">
+        <v>9</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>44211</v>
+      </c>
+      <c r="B37" s="1">
+        <v>44681</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1700</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37">
+        <v>8</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>43862</v>
+      </c>
+      <c r="B38" s="1">
+        <v>44227</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38">
+        <v>8</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>43160</v>
+      </c>
+      <c r="B39" s="1">
+        <v>43646</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1100</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>8</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>43647</v>
+      </c>
+      <c r="B40" s="1">
+        <v>44196</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1400</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40">
+        <v>9</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>44211</v>
+      </c>
+      <c r="B41" s="1">
+        <v>44681</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1700</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41">
+        <v>8</v>
+      </c>
+      <c r="F41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>43862</v>
+      </c>
+      <c r="B42" s="1">
+        <v>44227</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42">
+        <v>8</v>
+      </c>
+      <c r="F42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>44682</v>
+      </c>
+      <c r="B43" s="1">
+        <v>45169</v>
+      </c>
+      <c r="C43" s="2">
+        <v>2200</v>
+      </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+      <c r="E43">
+        <v>9</v>
+      </c>
+      <c r="F43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>42979</v>
+      </c>
+      <c r="B44" s="1">
+        <v>43465</v>
+      </c>
+      <c r="C44" s="2">
+        <v>900</v>
+      </c>
+      <c r="D44">
+        <v>6</v>
+      </c>
+      <c r="E44">
+        <v>9</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>43475</v>
+      </c>
+      <c r="B45" s="1">
+        <v>43905</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D45">
+        <v>7</v>
+      </c>
+      <c r="E45">
+        <v>9</v>
+      </c>
+      <c r="F45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>44348</v>
+      </c>
+      <c r="B46" s="1">
+        <v>44957</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1900</v>
+      </c>
+      <c r="D46">
+        <v>8</v>
+      </c>
+      <c r="E46">
+        <v>8</v>
+      </c>
+      <c r="F46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>42461</v>
+      </c>
+      <c r="B47" s="1">
+        <v>43039</v>
+      </c>
+      <c r="C47" s="2">
+        <v>800</v>
+      </c>
+      <c r="D47">
+        <v>9</v>
+      </c>
+      <c r="E47">
+        <v>9</v>
+      </c>
+      <c r="F47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>44958</v>
+      </c>
+      <c r="B48" s="1">
+        <v>45443</v>
+      </c>
+      <c r="C48" s="2">
+        <v>2500</v>
+      </c>
+      <c r="D48">
+        <v>10</v>
+      </c>
+      <c r="E48">
+        <v>9</v>
+      </c>
+      <c r="F48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>42979</v>
+      </c>
+      <c r="B49" s="1">
+        <v>43465</v>
+      </c>
+      <c r="C49" s="2">
+        <v>900</v>
+      </c>
+      <c r="D49">
+        <v>6</v>
+      </c>
+      <c r="E49">
+        <v>9</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>43475</v>
+      </c>
+      <c r="B50" s="1">
+        <v>43905</v>
+      </c>
+      <c r="C50" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D50">
+        <v>7</v>
+      </c>
+      <c r="E50">
+        <v>9</v>
+      </c>
+      <c r="F50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>44211</v>
+      </c>
+      <c r="B51" s="1">
+        <v>44681</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1700</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51">
+        <v>8</v>
+      </c>
+      <c r="F51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>43862</v>
+      </c>
+      <c r="B52" s="1">
+        <v>44227</v>
+      </c>
+      <c r="C52" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D52">
+        <v>4</v>
+      </c>
+      <c r="E52">
+        <v>8</v>
+      </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>44682</v>
+      </c>
+      <c r="B53" s="1">
+        <v>45169</v>
+      </c>
+      <c r="C53" s="2">
+        <v>2200</v>
+      </c>
+      <c r="D53">
+        <v>5</v>
+      </c>
+      <c r="E53">
+        <v>9</v>
+      </c>
+      <c r="F53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>42979</v>
+      </c>
+      <c r="B54" s="1">
+        <v>43465</v>
+      </c>
+      <c r="C54" s="2">
+        <v>900</v>
+      </c>
+      <c r="D54">
+        <v>6</v>
+      </c>
+      <c r="E54">
+        <v>9</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>43475</v>
+      </c>
+      <c r="B55" s="1">
+        <v>43905</v>
+      </c>
+      <c r="C55" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D55">
+        <v>7</v>
+      </c>
+      <c r="E55">
+        <v>9</v>
+      </c>
+      <c r="F55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>44348</v>
+      </c>
+      <c r="B56" s="1">
+        <v>44957</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1900</v>
+      </c>
+      <c r="D56">
+        <v>8</v>
+      </c>
+      <c r="E56">
+        <v>8</v>
+      </c>
+      <c r="F56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>42461</v>
+      </c>
+      <c r="B57" s="1">
+        <v>43039</v>
+      </c>
+      <c r="C57" s="2">
+        <v>800</v>
+      </c>
+      <c r="D57">
+        <v>9</v>
+      </c>
+      <c r="E57">
+        <v>9</v>
+      </c>
+      <c r="F57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>44958</v>
+      </c>
+      <c r="B58" s="1">
+        <v>45443</v>
+      </c>
+      <c r="C58" s="2">
+        <v>2500</v>
+      </c>
+      <c r="D58">
+        <v>10</v>
+      </c>
+      <c r="E58">
+        <v>9</v>
+      </c>
+      <c r="F58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>42979</v>
+      </c>
+      <c r="B59" s="1">
+        <v>43465</v>
+      </c>
+      <c r="C59" s="2">
+        <v>900</v>
+      </c>
+      <c r="D59">
+        <v>6</v>
+      </c>
+      <c r="E59">
+        <v>9</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>43475</v>
+      </c>
+      <c r="B60" s="1">
+        <v>43905</v>
+      </c>
+      <c r="C60" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D60">
+        <v>7</v>
+      </c>
+      <c r="E60">
+        <v>9</v>
+      </c>
+      <c r="F60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>44211</v>
+      </c>
+      <c r="B61" s="1">
+        <v>44681</v>
+      </c>
+      <c r="C61" s="2">
+        <v>1700</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61">
+        <v>8</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>43862</v>
+      </c>
+      <c r="B62" s="1">
+        <v>44227</v>
+      </c>
+      <c r="C62" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62">
+        <v>8</v>
+      </c>
+      <c r="F62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>42461</v>
+      </c>
+      <c r="B63" s="1">
+        <v>43039</v>
+      </c>
+      <c r="C63" s="2">
+        <v>800</v>
+      </c>
+      <c r="D63">
+        <v>9</v>
+      </c>
+      <c r="E63">
+        <v>9</v>
+      </c>
+      <c r="F63">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>44958</v>
+      </c>
+      <c r="B64" s="1">
+        <v>45443</v>
+      </c>
+      <c r="C64" s="2">
+        <v>2500</v>
+      </c>
+      <c r="D64">
+        <v>10</v>
+      </c>
+      <c r="E64">
+        <v>9</v>
+      </c>
+      <c r="F64">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>42979</v>
+      </c>
+      <c r="B65" s="1">
+        <v>43465</v>
+      </c>
+      <c r="C65" s="2">
+        <v>900</v>
+      </c>
+      <c r="D65">
+        <v>6</v>
+      </c>
+      <c r="E65">
+        <v>9</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>43475</v>
+      </c>
+      <c r="B66" s="1">
+        <v>43905</v>
+      </c>
+      <c r="C66" s="2">
+        <v>1200</v>
+      </c>
+      <c r="D66">
+        <v>7</v>
+      </c>
+      <c r="E66">
+        <v>9</v>
+      </c>
+      <c r="F66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>44211</v>
+      </c>
+      <c r="B67" s="1">
+        <v>44681</v>
+      </c>
+      <c r="C67" s="2">
+        <v>1700</v>
+      </c>
+      <c r="D67">
+        <v>3</v>
+      </c>
+      <c r="E67">
+        <v>8</v>
+      </c>
+      <c r="F67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>43862</v>
+      </c>
+      <c r="B68" s="1">
+        <v>44227</v>
+      </c>
+      <c r="C68" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+      <c r="E68">
+        <v>8</v>
+      </c>
+      <c r="F68">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
